--- a/slots/resources/sample/GiftList.xlsx
+++ b/slots/resources/sample/GiftList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GiftList" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,48 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1表示拜访赠送
+2表示房间内道具互动</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
   <si>
     <t>序列ID</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>名称多语言ID</t>
   </si>
   <si>
@@ -59,6 +95,9 @@
     <t>id</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -129,6 +168,102 @@
   </si>
   <si>
     <t>1990000_1000</t>
+  </si>
+  <si>
+    <t>点赞</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>lt_hddj_dz</t>
+  </si>
+  <si>
+    <t>握手</t>
+  </si>
+  <si>
+    <t>lt_hddj_ws</t>
+  </si>
+  <si>
+    <t>鼓掌</t>
+  </si>
+  <si>
+    <t>lt_hddj_gz</t>
+  </si>
+  <si>
+    <t>爱心</t>
+  </si>
+  <si>
+    <t>1980000_10</t>
+  </si>
+  <si>
+    <t>lt_hddj_ax</t>
+  </si>
+  <si>
+    <t>飞吻</t>
+  </si>
+  <si>
+    <t>lt_hddj_fw</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>lt_hddj_pj</t>
+  </si>
+  <si>
+    <t>巧克力</t>
+  </si>
+  <si>
+    <t>lt_hddj_qkl</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>lt_hddj_kf</t>
+  </si>
+  <si>
+    <t>玫瑰</t>
+  </si>
+  <si>
+    <t>lt_hddj_mg</t>
+  </si>
+  <si>
+    <t>跑车</t>
+  </si>
+  <si>
+    <t>lt_hddj_pc</t>
+  </si>
+  <si>
+    <t>扔袜子</t>
+  </si>
+  <si>
+    <t>lt_hddj_rwz</t>
+  </si>
+  <si>
+    <t>扔鸡蛋</t>
+  </si>
+  <si>
+    <t>lt_hddj_rjd</t>
+  </si>
+  <si>
+    <t>扔番茄</t>
+  </si>
+  <si>
+    <t>lt_hddj_rfq</t>
+  </si>
+  <si>
+    <t>扔乌龟</t>
+  </si>
+  <si>
+    <t>lt_hddj_rwg</t>
+  </si>
+  <si>
+    <t>扔炸弹</t>
+  </si>
+  <si>
+    <t>lt_hddj_rzd</t>
   </si>
 </sst>
 </file>
@@ -141,7 +276,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +433,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1306,16 +1452,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.625" customWidth="1"/>
-    <col min="4" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="23.5" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="2" max="3" width="13.625" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="23.5" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1331,50 +1477,59 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1382,199 +1537,486 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="1">
         <v>4057156</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4057157</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4057158</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1">
         <v>15</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4057159</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4057160</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4057161</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="1">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4057162</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>1008</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4057163</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4057164</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="1">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4057165</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="1">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
-        <v>4057157</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4057158</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1">
-        <v>4057159</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1">
-        <v>5</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1">
-        <v>4057160</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4057161</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="1">
-        <v>15</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4057162</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="1">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4057163</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="1">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1">
-        <v>4057164</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="1">
-        <v>15</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1">
-        <v>4057165</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="1">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <v>2002</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>2003</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
+        <v>2004</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1">
+        <v>2010</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1">
+        <v>2011</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="1">
+        <v>2012</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="1">
+        <v>2013</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="1">
+        <v>2014</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="1">
+        <v>2015</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/GiftList.xlsx
+++ b/slots/resources/sample/GiftList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="GiftList" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
   <si>
     <t>序列ID</t>
   </si>
@@ -116,16 +116,25 @@
     <t>1990000_100</t>
   </si>
   <si>
+    <t>bf_lwtb_1</t>
+  </si>
+  <si>
     <t>鲜花</t>
   </si>
   <si>
     <t>1990000_200</t>
   </si>
   <si>
+    <t>bf_lwtb_2</t>
+  </si>
+  <si>
     <t>饮品</t>
   </si>
   <si>
     <t>1990000_300</t>
+  </si>
+  <si>
+    <t>bf_lwtb_3</t>
   </si>
   <si>
     <t>曲奇</t>
@@ -435,12 +444,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1558,7 +1567,9 @@
       <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
@@ -1572,15 +1583,17 @@
         <v>4057157</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
@@ -1594,15 +1607,17 @@
         <v>4057158</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1">
         <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
@@ -1616,13 +1631,13 @@
         <v>4057159</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -1638,13 +1653,13 @@
         <v>4057160</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -1660,13 +1675,13 @@
         <v>4057161</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1">
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1682,13 +1697,13 @@
         <v>4057162</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1704,13 +1719,13 @@
         <v>4057163</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1726,13 +1741,13 @@
         <v>4057164</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1">
         <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1748,13 +1763,13 @@
         <v>4057165</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1">
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1767,13 +1782,13 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1784,13 +1799,13 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1801,13 +1816,13 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1818,13 +1833,13 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1835,13 +1850,13 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1852,13 +1867,13 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1869,13 +1884,13 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1886,13 +1901,13 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1903,13 +1918,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1920,13 +1935,13 @@
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1937,13 +1952,13 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1954,13 +1969,13 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1971,13 +1986,13 @@
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1988,13 +2003,13 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G28" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2005,13 +2020,13 @@
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/GiftList.xlsx
+++ b/slots/resources/sample/GiftList.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="GiftList" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -137,6 +138,102 @@
     <t>bf_lwtb_3</t>
   </si>
   <si>
+    <t>点赞</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>lt_hddj_dz</t>
+  </si>
+  <si>
+    <t>握手</t>
+  </si>
+  <si>
+    <t>lt_hddj_ws</t>
+  </si>
+  <si>
+    <t>鼓掌</t>
+  </si>
+  <si>
+    <t>lt_hddj_gz</t>
+  </si>
+  <si>
+    <t>爱心</t>
+  </si>
+  <si>
+    <t>1980000_10</t>
+  </si>
+  <si>
+    <t>lt_hddj_ax</t>
+  </si>
+  <si>
+    <t>飞吻</t>
+  </si>
+  <si>
+    <t>lt_hddj_fw</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>lt_hddj_pj</t>
+  </si>
+  <si>
+    <t>巧克力</t>
+  </si>
+  <si>
+    <t>lt_hddj_qkl</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>lt_hddj_kf</t>
+  </si>
+  <si>
+    <t>玫瑰</t>
+  </si>
+  <si>
+    <t>lt_hddj_mg</t>
+  </si>
+  <si>
+    <t>跑车</t>
+  </si>
+  <si>
+    <t>lt_hddj_pc</t>
+  </si>
+  <si>
+    <t>扔袜子</t>
+  </si>
+  <si>
+    <t>lt_hddj_rwz</t>
+  </si>
+  <si>
+    <t>扔鸡蛋</t>
+  </si>
+  <si>
+    <t>lt_hddj_rjd</t>
+  </si>
+  <si>
+    <t>扔番茄</t>
+  </si>
+  <si>
+    <t>lt_hddj_rfq</t>
+  </si>
+  <si>
+    <t>扔乌龟</t>
+  </si>
+  <si>
+    <t>lt_hddj_rwg</t>
+  </si>
+  <si>
+    <t>扔炸弹</t>
+  </si>
+  <si>
+    <t>lt_hddj_rzd</t>
+  </si>
+  <si>
     <t>曲奇</t>
   </si>
   <si>
@@ -177,102 +274,6 @@
   </si>
   <si>
     <t>1990000_1000</t>
-  </si>
-  <si>
-    <t>点赞</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>lt_hddj_dz</t>
-  </si>
-  <si>
-    <t>握手</t>
-  </si>
-  <si>
-    <t>lt_hddj_ws</t>
-  </si>
-  <si>
-    <t>鼓掌</t>
-  </si>
-  <si>
-    <t>lt_hddj_gz</t>
-  </si>
-  <si>
-    <t>爱心</t>
-  </si>
-  <si>
-    <t>1980000_10</t>
-  </si>
-  <si>
-    <t>lt_hddj_ax</t>
-  </si>
-  <si>
-    <t>飞吻</t>
-  </si>
-  <si>
-    <t>lt_hddj_fw</t>
-  </si>
-  <si>
-    <t>啤酒</t>
-  </si>
-  <si>
-    <t>lt_hddj_pj</t>
-  </si>
-  <si>
-    <t>巧克力</t>
-  </si>
-  <si>
-    <t>lt_hddj_qkl</t>
-  </si>
-  <si>
-    <t>咖啡</t>
-  </si>
-  <si>
-    <t>lt_hddj_kf</t>
-  </si>
-  <si>
-    <t>玫瑰</t>
-  </si>
-  <si>
-    <t>lt_hddj_mg</t>
-  </si>
-  <si>
-    <t>跑车</t>
-  </si>
-  <si>
-    <t>lt_hddj_pc</t>
-  </si>
-  <si>
-    <t>扔袜子</t>
-  </si>
-  <si>
-    <t>lt_hddj_rwz</t>
-  </si>
-  <si>
-    <t>扔鸡蛋</t>
-  </si>
-  <si>
-    <t>lt_hddj_rjd</t>
-  </si>
-  <si>
-    <t>扔番茄</t>
-  </si>
-  <si>
-    <t>lt_hddj_rfq</t>
-  </si>
-  <si>
-    <t>扔乌龟</t>
-  </si>
-  <si>
-    <t>lt_hddj_rwg</t>
-  </si>
-  <si>
-    <t>扔炸弹</t>
-  </si>
-  <si>
-    <t>lt_hddj_rzd</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1462,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="3" width="13.625" customWidth="1"/>
@@ -1622,221 +1623,186 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>1004</v>
+        <v>2001</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4057159</v>
-      </c>
-      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" s="1">
-        <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>1005</v>
+        <v>2002</v>
       </c>
       <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1">
-        <v>4057160</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>1006</v>
+        <v>2003</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4057161</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="1">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>1007</v>
+        <v>2004</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
-        <v>4057162</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="1">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>1008</v>
+        <v>2005</v>
       </c>
       <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1">
-        <v>4057163</v>
-      </c>
-      <c r="D12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="1">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>1009</v>
+        <v>2006</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4057164</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="1">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>1010</v>
+        <v>2007</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4057165</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="1">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G18" t="s">
         <v>48</v>
@@ -1844,7 +1810,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -1853,7 +1819,7 @@
         <v>49</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
         <v>50</v>
@@ -1861,7 +1827,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
@@ -1870,7 +1836,7 @@
         <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G20" t="s">
         <v>52</v>
@@ -1878,7 +1844,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -1887,7 +1853,7 @@
         <v>53</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -1895,7 +1861,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
@@ -1904,129 +1870,10 @@
         <v>55</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1">
-        <v>2009</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1">
-        <v>2010</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="D24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="1">
-        <v>2011</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1">
-        <v>2012</v>
-      </c>
-      <c r="B26" s="1">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>63</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1">
-        <v>2013</v>
-      </c>
-      <c r="B27" s="1">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1">
-        <v>2014</v>
-      </c>
-      <c r="B28" s="1">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
-        <v>67</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1">
-        <v>2015</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2034,4 +1881,163 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4057159</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4057160</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4057161</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4057162</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="1">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>1008</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4057163</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4057164</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="1">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4057165</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>